--- a/data/trans_orig/Q17B-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q17B-Provincia-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según número de veces que ha consultado al médico en las 2 últimas semanas</t>
+          <t>Número medio de veces que la población ha tenido una consulta médica en las 2 últimas semanas (tasa de respuesta: 99,19%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -721,22 +721,22 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,25; 0,5</t>
+          <t>0,24; 0,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,4</t>
+          <t>0,23; 0,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,31</t>
+          <t>0,19; 0,32</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,37</t>
+          <t>0,23; 0,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,36; 0,58</t>
+          <t>0,37; 0,59</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,32</t>
+          <t>0,23; 0,33</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -761,12 +761,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,33; 0,47</t>
+          <t>0,32; 0,48</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,31; 0,45</t>
+          <t>0,32; 0,46</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -856,22 +856,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,33</t>
+          <t>0,19; 0,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,31</t>
+          <t>0,2; 0,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,28</t>
+          <t>0,19; 0,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,32</t>
+          <t>0,17; 0,32</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,33</t>
+          <t>0,22; 0,32</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1006,22 +1006,22 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,33</t>
+          <t>0,22; 0,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,29</t>
+          <t>0,19; 0,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,26; 0,36</t>
+          <t>0,26; 0,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,46; 0,64</t>
+          <t>0,46; 0,65</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,39; 0,53</t>
+          <t>0,39; 0,52</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,3</t>
+          <t>0,22; 0,31</t>
         </is>
       </c>
     </row>
@@ -1136,17 +1136,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,12; 0,2</t>
+          <t>0,12; 0,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,21; 0,35</t>
+          <t>0,2; 0,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,26; 0,4</t>
+          <t>0,25; 0,39</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1161,27 +1161,27 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,34; 0,49</t>
+          <t>0,34; 0,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,36; 0,51</t>
+          <t>0,37; 0,53</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,31; 0,65</t>
+          <t>0,3; 0,64</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,21; 0,29</t>
+          <t>0,22; 0,29</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,3; 0,4</t>
+          <t>0,29; 0,4</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,55</t>
+          <t>0,29; 0,56</t>
         </is>
       </c>
     </row>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,27; 0,57</t>
+          <t>0,27; 0,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1296,12 +1296,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,41; 0,7</t>
+          <t>0,41; 0,71</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,43; 0,62</t>
+          <t>0,42; 0,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1311,12 +1311,12 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,12; 0,19</t>
+          <t>0,11; 0,19</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,34; 0,53</t>
+          <t>0,35; 0,53</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,49</t>
+          <t>0,29; 0,48</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,86; 1,45</t>
+          <t>0,86; 1,43</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,37; 0,51</t>
+          <t>0,38; 0,51</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,79; 1,13</t>
+          <t>0,77; 1,13</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,3</t>
+          <t>0,21; 0,3</t>
         </is>
       </c>
     </row>
@@ -1556,17 +1556,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,41</t>
+          <t>0,24; 0,4</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,25; 0,33</t>
+          <t>0,24; 0,32</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,26; 0,44</t>
+          <t>0,26; 0,43</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1581,22 +1581,22 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,35; 0,46</t>
+          <t>0,35; 0,45</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,26; 0,36</t>
+          <t>0,26; 0,37</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,48</t>
+          <t>0,17; 0,48</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,3; 0,41</t>
+          <t>0,3; 0,4</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -1606,12 +1606,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,27; 0,38</t>
+          <t>0,28; 0,38</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,21; 0,41</t>
+          <t>0,22; 0,41</t>
         </is>
       </c>
     </row>
@@ -1716,12 +1716,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,37; 0,48</t>
+          <t>0,38; 0,48</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,32; 0,48</t>
+          <t>0,31; 0,48</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,33; 0,41</t>
+          <t>0,33; 0,4</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,27</t>
+          <t>0,22; 0,27</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,39; 0,46</t>
+          <t>0,39; 0,45</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">

--- a/data/trans_orig/Q17B-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q17B-Provincia-trans_orig.xlsx
@@ -663,47 +663,47 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
+          <t>0,22</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,29</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,45</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0,46</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0,27</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>0,24</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,29</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,45</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,46</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0,27</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0,39</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>0,38</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,24</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0,39</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>0,38</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,26</t>
         </is>
       </c>
     </row>
@@ -721,37 +721,37 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,48</t>
+          <t>0,25; 0,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,41</t>
+          <t>0,23; 0,4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,32</t>
+          <t>0,17; 0,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,37</t>
+          <t>0,22; 0,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,36; 0,56</t>
+          <t>0,37; 0,56</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,37; 0,59</t>
+          <t>0,37; 0,57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,33</t>
+          <t>0,23; 0,32</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -761,7 +761,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,32; 0,48</t>
+          <t>0,33; 0,48</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,3</t>
+          <t>0,21; 0,28</t>
         </is>
       </c>
     </row>
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,27</t>
+          <t>0,26</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -856,17 +856,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,34</t>
+          <t>0,2; 0,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,32</t>
+          <t>0,2; 0,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,28</t>
+          <t>0,2; 0,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,27; 0,37</t>
+          <t>0,26; 0,37</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -886,12 +886,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,32; 0,44</t>
+          <t>0,32; 0,43</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,32</t>
+          <t>0,22; 0,31</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,21; 0,3</t>
+          <t>0,21; 0,29</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,28</t>
+          <t>0,29</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,26</t>
+          <t>0,27</t>
         </is>
       </c>
     </row>
@@ -996,27 +996,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,13; 0,22</t>
+          <t>0,13; 0,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,26; 0,46</t>
+          <t>0,27; 0,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,34</t>
+          <t>0,21; 0,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,29</t>
+          <t>0,19; 0,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,26; 0,37</t>
+          <t>0,26; 0,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,35</t>
+          <t>0,24; 0,35</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,39; 0,52</t>
+          <t>0,39; 0,53</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,31</t>
+          <t>0,23; 0,31</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,43</t>
+          <t>0,35</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,37</t>
+          <t>0,32</t>
         </is>
       </c>
     </row>
@@ -1136,17 +1136,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,12; 0,21</t>
+          <t>0,12; 0,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,35</t>
+          <t>0,21; 0,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,25; 0,39</t>
+          <t>0,26; 0,39</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1166,12 +1166,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 0,53</t>
+          <t>0,37; 0,51</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,3; 0,64</t>
+          <t>0,3; 0,42</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,4</t>
+          <t>0,29; 0,39</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,56</t>
+          <t>0,28; 0,37</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,11</t>
+          <t>0,1</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,14</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,13</t>
+          <t>0,12</t>
         </is>
       </c>
     </row>
@@ -1276,32 +1276,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,47</t>
+          <t>0,23; 0,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,27; 0,56</t>
+          <t>0,27; 0,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,21</t>
+          <t>0,11; 0,21</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,15</t>
+          <t>0,07; 0,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,41; 0,71</t>
+          <t>0,41; 0,7</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,42; 0,62</t>
+          <t>0,42; 0,61</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1311,17 +1311,17 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,19</t>
+          <t>0,11; 0,18</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,35; 0,53</t>
+          <t>0,35; 0,54</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,37; 0,55</t>
+          <t>0,38; 0,53</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,16</t>
+          <t>0,1; 0,15</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,22</t>
+          <t>0,21</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1421,32 +1421,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,31; 0,5</t>
+          <t>0,32; 0,51</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,59; 0,98</t>
+          <t>0,58; 0,96</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,27</t>
+          <t>0,17; 0,26</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,48</t>
+          <t>0,29; 0,5</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,41; 0,56</t>
+          <t>0,4; 0,56</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,86; 1,43</t>
+          <t>0,91; 1,49</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,33</t>
+          <t>0,22; 0,34</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,77; 1,13</t>
+          <t>0,78; 1,13</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,21; 0,3</t>
+          <t>0,21; 0,29</t>
         </is>
       </c>
     </row>
@@ -1503,47 +1503,47 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
+          <t>0,31</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,39</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,4</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0,31</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>0,49</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0,34</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>0,34</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
           <t>0,32</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,39</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,4</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,31</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>0,35</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>0,34</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0,34</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>0,32</t>
-        </is>
-      </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,34</t>
+          <t>0,41</t>
         </is>
       </c>
     </row>
@@ -1556,22 +1556,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,4</t>
+          <t>0,24; 0,38</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,32</t>
+          <t>0,24; 0,33</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,26; 0,43</t>
+          <t>0,26; 0,44</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,26; 0,4</t>
+          <t>0,25; 0,39</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1581,22 +1581,22 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,35; 0,45</t>
+          <t>0,35; 0,46</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,26; 0,37</t>
+          <t>0,27; 0,37</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,48</t>
+          <t>0,43; 0,59</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,3; 0,4</t>
+          <t>0,3; 0,41</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -1606,12 +1606,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,28; 0,38</t>
+          <t>0,28; 0,39</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,41</t>
+          <t>0,36; 0,46</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,18</t>
+          <t>0,23</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0,33</t>
+          <t>0,31</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0,24</t>
+          <t>0,27</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,26; 0,35</t>
+          <t>0,26; 0,36</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1706,17 +1706,17 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,26; 0,35</t>
+          <t>0,27; 0,35</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,25</t>
+          <t>0,2; 0,27</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,38; 0,48</t>
+          <t>0,37; 0,48</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,38</t>
+          <t>0,28; 0,35</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1746,12 +1746,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,3; 0,35</t>
+          <t>0,3; 0,36</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,29</t>
+          <t>0,25; 0,3</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>0,23</t>
+          <t>0,24</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1803,14 +1803,14 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
+          <t>0,33</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
           <t>0,31</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>0,31</t>
-        </is>
-      </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
           <t>0,35</t>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,27</t>
+          <t>0,29</t>
         </is>
       </c>
     </row>
@@ -1846,12 +1846,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,35</t>
+          <t>0,3; 0,35</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,26</t>
+          <t>0,22; 0,27</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1861,17 +1861,17 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
+          <t>0,39; 0,44</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
           <t>0,39; 0,45</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>0,39; 0,45</t>
-        </is>
-      </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,26; 0,35</t>
+          <t>0,31; 0,35</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,3</t>
+          <t>0,27; 0,3</t>
         </is>
       </c>
     </row>
